--- a/www/download/IND.capital_depreciation.s.us.zdW16.xlsx
+++ b/www/download/IND.capital_depreciation.s.us.zdW16.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,72 +688,72 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -760,7 +765,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,72 +775,72 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -847,7 +852,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,72 +862,72 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -934,7 +939,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,72 +949,72 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1021,7 +1026,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,72 +1036,72 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.438</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>0.529</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1108,7 +1113,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,72 +1123,72 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1195,7 +1200,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,72 +1210,72 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1.063</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.487</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1.883</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2.225</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2.549</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1282,7 +1287,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,72 +1297,72 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1369,7 +1374,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,72 +1384,72 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1456,7 +1461,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,72 +1471,72 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.463</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.592</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.684</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0.839</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>0.856</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>0.908</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1543,7 +1548,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,72 +1558,72 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -1630,7 +1635,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,72 +1645,72 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -1717,7 +1722,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,72 +1732,72 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -1804,7 +1809,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,72 +1819,72 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -1891,7 +1896,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,72 +1906,72 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.359</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.401</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.513</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.519</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -1978,7 +1983,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,72 +1993,72 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.426</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.515</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.528</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2065,7 +2070,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,72 +2080,72 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2152,7 +2157,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,72 +2167,72 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2239,7 +2244,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,72 +2254,72 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2326,7 +2331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,72 +2341,72 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>0.401</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>0.506</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2413,7 +2418,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,72 +2428,72 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2500,7 +2505,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,72 +2515,72 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>0.484</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -2587,7 +2592,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,72 +2602,72 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.182</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.106</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.084</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.262</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1.237</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1.173</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1.167</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1.326</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1.646</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1.784</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1.762</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -2674,7 +2679,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,72 +2689,72 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0.359</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -2761,7 +2766,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,72 +2776,72 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -2848,7 +2853,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,72 +2863,72 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -2935,7 +2940,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,72 +2950,72 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3022,7 +3027,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,72 +3037,72 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3109,7 +3114,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,72 +3124,72 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3196,7 +3201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,72 +3211,72 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3283,7 +3288,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,72 +3298,72 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3370,7 +3375,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,72 +3385,72 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -3457,7 +3462,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,72 +3472,72 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -3544,7 +3549,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,72 +3559,72 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>0.396</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -3631,7 +3636,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,72 +3646,72 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -3718,7 +3723,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,72 +3733,72 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -3805,7 +3810,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,72 +3820,72 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -3892,7 +3897,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,72 +3907,72 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -3979,7 +3984,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,72 +3994,72 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4066,7 +4071,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,72 +4081,72 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2.667</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2.773</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2.805</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2.905</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>3.146</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>3.427</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>3.758</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>4.087</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>4.371</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>4.427</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>4.897</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>5.008</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>5.138</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4153,7 +4158,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,72 +4168,72 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.782</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.767</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0.877</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1.054</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1.284</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>1.886</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>1.772</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2.131</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>2.469</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2.604</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2.596</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4240,7 +4245,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,72 +4255,72 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>7.847</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>7.883</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>9.075</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>11.179</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>12.088</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>13.542</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>15.266</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>15.267</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>16.766</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>19.178</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>19.561</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4327,7 +4332,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4337,72 +4342,72 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -4414,7 +4419,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4424,72 +4429,72 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -4501,7 +4506,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,72 +4516,72 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -4588,7 +4593,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4600,7 +4605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4612,7 +4617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4624,7 +4629,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4641,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4648,7 +4653,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4695,6 +4700,11 @@
           <t>capital_depreciation.s.us</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4729,6 +4739,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
